--- a/new_spreadsheet.xlsx
+++ b/new_spreadsheet.xlsx
@@ -7,7 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="W-2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pay Stub YTD" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1099-R" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ESPP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Investment Income" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Deductions &amp; Payments" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +31,43 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -42,12 +75,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +497,2065 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2025 TAX SUMMARY</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>INCOME</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>W-2 Income</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Wages, Tips (Box 1)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>596090</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>W-2 Income</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Medicare Wages (Box 5)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>615526.48</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>1099-R</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Rollover / Distribution</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>48113.31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>1099-DIV</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Total Ordinary Dividends</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>163.47</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>1099-DIV</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Qualified Dividends</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>163.47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>1099-INT</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>1099-B</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Proceeds from Sales</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>92865.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>1099-B</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Cost Basis (Covered)</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>32103.19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>ESPP</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Taxable Gain</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>6754</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TAXES WITHHELD</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Federal Income Tax Withheld (Box 2)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>126173.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Social Security Tax (Box 4)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>10918.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Medicare Tax (Box 6)</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>12664.87</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>State Income Tax - CA (Box 17)</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>55412.61</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Estimated Payments</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>IRS Estimated Tax Payments</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>47460</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>401(k)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Pre-Tax 401(k) Contributions</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>26310</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>401(k)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>401(k) Catch-Up</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>4620.36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>401(k)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>After-Tax 401(k)</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>26722.56</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>HSA</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Employee HSA Contributions (Box 12 W)</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>9550</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Property Tax</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Property Tax Paid</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>19326.74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Charitable</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Charitable Contributions</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>ESPP</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>ESPP Contributions</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>25835.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A3:C3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>W-2 WAGE AND TAX STATEMENT — 2025</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Employer / Filing Info</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Employer</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>SentinelOne, Inc.</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Employer Address</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>444 Castro Street, 4th Floor, Mountain View, CA 94041</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>EIN</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>99-0385461</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>State ID</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>031-5193-3</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Retirement Plan</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Yes (Box 13 checked)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Filing Status (Federal)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Married Filing Jointly</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Filing Status (State)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Single or Married w/ 2+ Incomes</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Box</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Box 1</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Wages, Tips, Other Compensation</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>596090</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Box 2</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Federal Income Tax Withheld</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>126173.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Box 3</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Social Security Wages</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>176100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Box 4</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Social Security Tax Withheld</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>10918.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Box 5</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Medicare Wages and Tips</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>615526.48</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Box 6</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Medicare Tax Withheld</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>12664.87</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Box 12a</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>C — Taxable Cost of Group-Term Life</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Box 12b</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>D — 401(k) Elective Deferrals</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>26190.48</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Box 12c</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>W — Employer HSA Contributions</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Box 12d</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>DD — Cost of Employer-Sponsored Health</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>8054.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Box 14</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>After Tax</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>49417.67</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Box 14</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>CASDI</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>7412.96</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Box 14</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>ESPP</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>6754</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Box 14</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>RSU</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>262011.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Box 16</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>State Wages (CA)</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>599690</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Box 17</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>State Income Tax Withheld (CA)</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>55412.61</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PAY STUB — YEAR TO DATE (Period: 12/16/2025 – 12/31/2025)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>YTD Totals</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Hours Worked YTD</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="11" t="n">
+        <v>2080.08</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Gross Pay YTD</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="8" t="n">
+        <v>309786.83</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Pre-Tax Deductions YTD</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="8" t="n">
+        <v>41390</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Employee Taxes YTD</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="8" t="n">
+        <v>95295.11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Post-Tax Deductions YTD</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="8" t="n">
+        <v>92683.07000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Net Pay YTD</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="8" t="n">
+        <v>80418.64999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Earnings YTD</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="8" t="n">
+        <v>215512.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Annual Performance Bonus</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="8" t="n">
+        <v>31731.07</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Restricted Stock Unit Gain</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="8" t="n">
+        <v>62543.26</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Group Term Life</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="8" t="n">
+        <v>2300.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Total Earnings YTD</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="8" t="n">
+        <v>312086.93</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Employee Taxes YTD</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Federal Withholding</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="8" t="n">
+        <v>52838.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Social Security (OASDI)</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="8" t="n">
+        <v>10918.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="8" t="n">
+        <v>5289.88</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>State Tax — CA</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="8" t="n">
+        <v>24135.23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>CA VDI (CAVDI)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="8" t="n">
+        <v>2113.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Total Employee Taxes YTD</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="8" t="n">
+        <v>95295.11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Pre-Tax Deductions YTD</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>401(k)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="8" t="n">
+        <v>11687.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>401(k) Catch-Up</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="8" t="n">
+        <v>4620.36</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>401(k) Annual Perf Bonus/Commission</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="8" t="n">
+        <v>11812.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>401(k) Annual Perf Bonus Catch-Up</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="8" t="n">
+        <v>2879.64</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>EE Health Savings Account (HSA)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="8" t="n">
+        <v>9550</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="8" t="n">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="8" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Total Pre-Tax Deductions YTD</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="8" t="n">
+        <v>41390</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Post-Tax Deductions YTD</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>401(k) After Tax</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="8" t="n">
+        <v>26722.56</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>401(k) After Tax — Annual Perf Bonus/Commission</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="8" t="n">
+        <v>9407.74</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>ESPP 12/01/24 – 05/31/25</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="8" t="n">
+        <v>7823.9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>ESPP 06/01/25 – 11/30/25</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="8" t="n">
+        <v>8655.719999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>ESPP 12/01/25 – 05/31/26</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="8" t="n">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>RSU After-Tax Offset</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="8" t="n">
+        <v>38624.15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Total Post-Tax Deductions YTD</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="8" t="n">
+        <v>92683.07000000001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Employer Paid Benefits YTD</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>401(k) Employer Match</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="8" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="40">
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A39:B39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FORM 1099-R — DISTRIBUTIONS FROM PENSIONS, ANNUITIES, ETC. — 2025</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Gross Distribution</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>48113.31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Taxable Amount</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Capital Gain</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Federal Income Tax Withheld</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Employee Contrib / Designated Roth / Insurance</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>48113.31</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Net Unrealized Appreciation</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Distribution Code</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>G (Direct Rollover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>State Tax Withheld</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Payer's State No.</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>80275704</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>State Distribution</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ESPP — SENTINELONE, INC. — 2025</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Account Number</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>146585942</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>SENTINELONE, INC. (S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>ESPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Grant Date</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>07-08-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Purchase Begin Date</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>07-08-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Purchase Date</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>01-03-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Shares Purchased</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Previous Carry Forward</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Current Contributions</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>25835.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Total Contributions</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>25835.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Total Purchase Price</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>21256.68</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Amount Refunded</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>4578.57</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Total Value at Purchase</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>28010.68</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Taxable Gain</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>6754</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Grant Date Market Value / Share</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>20.36</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Purchase Value / Share</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>22.81</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Purchase Price / Share (85% of Grant Date MV)</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>17.31</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>INVESTMENT INCOME — 1099-DIV / 1099-INT / 1099-B — 2025</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>1099-DIV — Dividends</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1a  Total Ordinary Dividends</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>163.47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1b  Qualified Dividends</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>163.47</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>All Other Boxes</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>1099-INT — Interest</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>All Other Boxes</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>1099-MISC</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>All Boxes</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>1099-OID</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>All Boxes</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>1099-B — Proceeds from Broker Transactions</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>1d  Total Proceeds</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>92865.05</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Covered Securities</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>40730.42</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Noncovered Securities</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>52134.63</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>1e  Cost Basis (Covered)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>32103.19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>1f  Accrued Market Discount</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>1g  Wash Sale Loss Disallowed</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Federal Income Tax Withheld</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DEDUCTIONS &amp; TAX PAYMENTS — 2025</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Tax Payments</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>IRS Estimated Tax Payments</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>47460</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Itemized Deductions</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Property Tax</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>19326.74</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Charitable Contributions</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Retirement Contributions</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>401(k) Pre-Tax (Employee)</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>11687.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>401(k) Catch-Up</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>4620.36</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>401(k) Annual Perf Bonus/Commission</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>11812.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>401(k) Annual Perf Bonus Catch-Up</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>2879.64</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>401(k) After-Tax (Employee)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>26722.56</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>401(k) After-Tax — Annual Perf Bonus</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>9407.74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>401(k) Employer Match</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Health / Other Pre-Tax</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>HSA Employee Contribution</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>9550</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Dental</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>204</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A9:B9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>